--- a/Beduerfnisse.xlsx
+++ b/Beduerfnisse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proj\Produktentwicklung\PE1_PE2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873B7AD2-1C35-44F6-A094-A765DC90FB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADE03375-860F-4DEA-80F8-4B316B41D7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="584" xr2:uid="{47443944-8BAF-4C53-B4C6-99A39F8AAB55}"/>
+    <workbookView xWindow="-132" yWindow="-132" windowWidth="23304" windowHeight="12504" tabRatio="505" xr2:uid="{47443944-8BAF-4C53-B4C6-99A39F8AAB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Beduerfnisse_final" sheetId="5" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="257">
   <si>
     <t>Bereich</t>
   </si>
@@ -815,6 +815,9 @@
   </si>
   <si>
     <t>analytisch, besserwisserisch, kritisch, klug, weise, intellektuell</t>
+  </si>
+  <si>
+    <t>Macht &amp; Status</t>
   </si>
 </sst>
 </file>
@@ -884,10 +887,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -895,6 +898,55 @@
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -957,55 +1009,6 @@
         <scheme val="minor"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1087,25 +1090,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{40589C40-73B7-4612-8319-3F0D6819D29A}" name="Tabelle4" displayName="Tabelle4" ref="B1:D30" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{40589C40-73B7-4612-8319-3F0D6819D29A}" name="Tabelle4" displayName="Tabelle4" ref="B1:D30" totalsRowShown="0" headerRowDxfId="15">
   <autoFilter ref="B1:D30" xr:uid="{40589C40-73B7-4612-8319-3F0D6819D29A}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{93F116B5-BD77-4241-BEAF-7A5C8E23159C}" name="Bedürfnis" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{1EEA4BB5-AE54-4130-83CB-3178360907D7}" name="Eigenschaft" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{5893CD28-82C8-44B7-BEB4-74F465D62BC1}" name="Handlung" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{93F116B5-BD77-4241-BEAF-7A5C8E23159C}" name="Bedürfnis" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{1EEA4BB5-AE54-4130-83CB-3178360907D7}" name="Eigenschaft" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{5893CD28-82C8-44B7-BEB4-74F465D62BC1}" name="Handlung" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C523C800-CF86-4F24-BFDE-371AC6C54775}" name="Tabelle2" displayName="Tabelle2" ref="A1:E77" totalsRowShown="0" headerRowDxfId="10" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C523C800-CF86-4F24-BFDE-371AC6C54775}" name="Tabelle2" displayName="Tabelle2" ref="A1:E77" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
   <autoFilter ref="A1:E77" xr:uid="{279D9105-C626-4ED2-AE24-08E5CB5A9C68}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AFD38166-0CBD-4415-ABD5-1DCB2D633E6F}" name="Adjektiv" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{EB491063-0DB6-4450-913D-FFCE147DE062}" name="Bedürfnis 1" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{513422E1-DAAB-4761-8C09-0A33F15BCC74}" name="Bedürfnis 2" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{2243AA71-7F32-4D80-96A9-3399AE46984D}" name="Bemerkung" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{AFD38166-0CBD-4415-ABD5-1DCB2D633E6F}" name="Adjektiv" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{EB491063-0DB6-4450-913D-FFCE147DE062}" name="Bedürfnis 1" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{513422E1-DAAB-4761-8C09-0A33F15BCC74}" name="Bedürfnis 2" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{2243AA71-7F32-4D80-96A9-3399AE46984D}" name="Bemerkung" dataDxfId="6"/>
     <tableColumn id="5" xr3:uid="{DA4C8D55-9D60-4E06-8516-CC775A7E3BA8}" name="Entscheidung"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1113,13 +1116,13 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{034A0C3B-BD2D-4404-8476-8598A0F3B33A}" name="Tabelle3" displayName="Tabelle3" ref="A1:D41" totalsRowShown="0" headerRowDxfId="4" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{034A0C3B-BD2D-4404-8476-8598A0F3B33A}" name="Tabelle3" displayName="Tabelle3" ref="A1:D41" totalsRowShown="0" headerRowDxfId="5" dataDxfId="4">
   <autoFilter ref="A1:D41" xr:uid="{034A0C3B-BD2D-4404-8476-8598A0F3B33A}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0B4FBE35-9722-464D-A89A-B0BBCE16BFB4}" name="Adjektiv" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{C2B2F9CA-BDB0-4B2C-B38A-0018C21934E3}" name="Bedürfnis 1" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{FF613F87-9AAB-4DB5-BDCD-1F832BE4FADE}" name="Bedürfnis 2" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{504765EB-5ACC-4A67-B71A-D1CCA0741297}" name="Bemerkung" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{0B4FBE35-9722-464D-A89A-B0BBCE16BFB4}" name="Adjektiv" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{C2B2F9CA-BDB0-4B2C-B38A-0018C21934E3}" name="Bedürfnis 1" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{FF613F87-9AAB-4DB5-BDCD-1F832BE4FADE}" name="Bedürfnis 2" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{504765EB-5ACC-4A67-B71A-D1CCA0741297}" name="Bemerkung" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1443,21 +1446,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{226F3C7F-FD1E-44F1-A95B-59582220DD13}">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="60.109375" customWidth="1"/>
-    <col min="4" max="4" width="50.21875" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="56.90625" customWidth="1"/>
+    <col min="4" max="4" width="50.1796875" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="25.6328125" style="6" customWidth="1"/>
     <col min="8" max="8" width="28" style="6" customWidth="1"/>
     <col min="9" max="9" width="31" style="6" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" style="6" customWidth="1"/>
-    <col min="11" max="12" width="15.77734375" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" style="6" customWidth="1"/>
+    <col min="11" max="12" width="15.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1475,7 +1478,7 @@
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1493,7 +1496,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1511,7 +1514,7 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
     </row>
-    <row r="4" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1529,7 +1532,7 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1547,7 +1550,7 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -1565,7 +1568,7 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -1583,7 +1586,7 @@
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
     </row>
-    <row r="8" spans="1:9" ht="112.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="112.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1601,7 +1604,7 @@
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1619,7 +1622,7 @@
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -1637,9 +1640,9 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>25</v>
@@ -1655,9 +1658,9 @@
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
     </row>
-    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>27</v>
@@ -1673,9 +1676,9 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
-    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>29</v>
@@ -1691,9 +1694,9 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
-    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>24</v>
+        <v>256</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>31</v>
@@ -1709,9 +1712,9 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
     </row>
-    <row r="15" spans="1:9" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="88.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>256</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>34</v>
@@ -1727,9 +1730,9 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
     </row>
-    <row r="16" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>256</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>36</v>
@@ -1745,9 +1748,9 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
-    <row r="17" spans="1:9" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="43.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>256</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>38</v>
@@ -1763,9 +1766,9 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
     </row>
-    <row r="18" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>256</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>40</v>
@@ -1781,9 +1784,9 @@
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>256</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>42</v>
@@ -1799,7 +1802,7 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
@@ -1817,7 +1820,7 @@
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>44</v>
       </c>
@@ -1835,7 +1838,7 @@
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
     </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>49</v>
       </c>
@@ -1853,7 +1856,7 @@
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
     </row>
-    <row r="23" spans="1:9" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="64.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -1871,7 +1874,7 @@
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>52</v>
       </c>
@@ -1889,7 +1892,7 @@
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
     </row>
-    <row r="25" spans="1:9" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>52</v>
       </c>
@@ -1907,7 +1910,7 @@
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
     </row>
-    <row r="26" spans="1:9" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
@@ -1925,7 +1928,7 @@
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -1943,7 +1946,7 @@
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
@@ -1961,7 +1964,7 @@
       <c r="H28" s="2"/>
       <c r="I28" s="2"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>64</v>
       </c>
@@ -1979,7 +1982,7 @@
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
     </row>
-    <row r="30" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
@@ -2009,21 +2012,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EF108D7-4CE3-4F60-87CA-40F102BF4FA2}">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.77734375" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" customWidth="1"/>
-    <col min="4" max="4" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.44140625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="25.6640625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" customWidth="1"/>
+    <col min="4" max="4" width="33.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.453125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="25.6328125" style="6" customWidth="1"/>
     <col min="8" max="8" width="28" style="6" customWidth="1"/>
     <col min="9" max="9" width="31" style="6" customWidth="1"/>
-    <col min="10" max="10" width="15.77734375" style="6" customWidth="1"/>
-    <col min="11" max="12" width="15.77734375" customWidth="1"/>
+    <col min="10" max="10" width="15.81640625" style="6" customWidth="1"/>
+    <col min="11" max="12" width="15.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2049,7 +2052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -2075,7 +2078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -2101,7 +2104,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
@@ -2127,7 +2130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -2153,7 +2156,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
@@ -2179,7 +2182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -2205,7 +2208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="112.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="112.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -2231,7 +2234,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -2257,7 +2260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>15</v>
       </c>
@@ -2283,7 +2286,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -2309,7 +2312,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>24</v>
       </c>
@@ -2335,7 +2338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -2361,7 +2364,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -2387,7 +2390,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="88.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="88.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>33</v>
       </c>
@@ -2413,7 +2416,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>33</v>
       </c>
@@ -2439,7 +2442,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="43.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>33</v>
       </c>
@@ -2465,7 +2468,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="46.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>33</v>
       </c>
@@ -2491,7 +2494,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>33</v>
       </c>
@@ -2517,7 +2520,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
@@ -2543,7 +2546,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>44</v>
       </c>
@@ -2569,7 +2572,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>49</v>
       </c>
@@ -2595,7 +2598,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="64.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="64.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -2621,7 +2624,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>52</v>
       </c>
@@ -2647,7 +2650,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>52</v>
       </c>
@@ -2673,7 +2676,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="34.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>52</v>
       </c>
@@ -2699,7 +2702,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>61</v>
       </c>
@@ -2725,7 +2728,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>64</v>
       </c>
@@ -2751,7 +2754,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>64</v>
       </c>
@@ -2777,7 +2780,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
@@ -2812,16 +2815,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C6B01A6-11F0-43C2-B0C8-CFC95CA48310}">
   <dimension ref="A1:F104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.77734375" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -2838,7 +2841,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>73</v>
       </c>
@@ -2853,7 +2856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>74</v>
       </c>
@@ -2868,7 +2871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>75</v>
       </c>
@@ -2883,7 +2886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>78</v>
       </c>
@@ -2898,7 +2901,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>83</v>
       </c>
@@ -2913,7 +2916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>86</v>
       </c>
@@ -2928,7 +2931,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>88</v>
       </c>
@@ -2943,7 +2946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>90</v>
       </c>
@@ -2958,7 +2961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>92</v>
       </c>
@@ -2973,7 +2976,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>93</v>
       </c>
@@ -2988,7 +2991,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>94</v>
       </c>
@@ -3003,7 +3006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>95</v>
       </c>
@@ -3018,7 +3021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>98</v>
       </c>
@@ -3033,7 +3036,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>101</v>
       </c>
@@ -3048,7 +3051,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>102</v>
       </c>
@@ -3063,7 +3066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>104</v>
       </c>
@@ -3078,7 +3081,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>106</v>
       </c>
@@ -3093,7 +3096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>107</v>
       </c>
@@ -3108,7 +3111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>108</v>
       </c>
@@ -3123,7 +3126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>110</v>
       </c>
@@ -3138,7 +3141,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>111</v>
       </c>
@@ -3153,7 +3156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>112</v>
       </c>
@@ -3168,7 +3171,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>113</v>
       </c>
@@ -3183,7 +3186,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>114</v>
       </c>
@@ -3198,7 +3201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>115</v>
       </c>
@@ -3213,7 +3216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>116</v>
       </c>
@@ -3228,7 +3231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>117</v>
       </c>
@@ -3243,7 +3246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>118</v>
       </c>
@@ -3258,7 +3261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>119</v>
       </c>
@@ -3273,7 +3276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>123</v>
       </c>
@@ -3288,7 +3291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>125</v>
       </c>
@@ -3303,7 +3306,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>132</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>133</v>
       </c>
@@ -3333,7 +3336,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>134</v>
       </c>
@@ -3348,7 +3351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>136</v>
       </c>
@@ -3363,7 +3366,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>138</v>
       </c>
@@ -3378,7 +3381,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>141</v>
       </c>
@@ -3393,7 +3396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>142</v>
       </c>
@@ -3408,7 +3411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>143</v>
       </c>
@@ -3423,7 +3426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>144</v>
       </c>
@@ -3438,7 +3441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>145</v>
       </c>
@@ -3453,7 +3456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>146</v>
       </c>
@@ -3468,7 +3471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>147</v>
       </c>
@@ -3483,7 +3486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>148</v>
       </c>
@@ -3498,7 +3501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>151</v>
       </c>
@@ -3513,7 +3516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>152</v>
       </c>
@@ -3528,7 +3531,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>154</v>
       </c>
@@ -3543,7 +3546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>155</v>
       </c>
@@ -3558,7 +3561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>156</v>
       </c>
@@ -3573,7 +3576,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>158</v>
       </c>
@@ -3588,7 +3591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>159</v>
       </c>
@@ -3603,7 +3606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>160</v>
       </c>
@@ -3618,7 +3621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>161</v>
       </c>
@@ -3633,7 +3636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>162</v>
       </c>
@@ -3648,7 +3651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>163</v>
       </c>
@@ -3663,7 +3666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>164</v>
       </c>
@@ -3678,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>165</v>
       </c>
@@ -3693,7 +3696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>166</v>
       </c>
@@ -3708,7 +3711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>167</v>
       </c>
@@ -3723,7 +3726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>168</v>
       </c>
@@ -3738,7 +3741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>169</v>
       </c>
@@ -3753,7 +3756,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>170</v>
       </c>
@@ -3768,7 +3771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>171</v>
       </c>
@@ -3783,7 +3786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>172</v>
       </c>
@@ -3798,7 +3801,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>173</v>
       </c>
@@ -3813,7 +3816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>174</v>
       </c>
@@ -3828,7 +3831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>175</v>
       </c>
@@ -3843,7 +3846,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>176</v>
       </c>
@@ -3858,7 +3861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>177</v>
       </c>
@@ -3873,7 +3876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>178</v>
       </c>
@@ -3888,7 +3891,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>179</v>
       </c>
@@ -3903,7 +3906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>180</v>
       </c>
@@ -3918,7 +3921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>217</v>
       </c>
@@ -3933,7 +3936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>218</v>
       </c>
@@ -3948,7 +3951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>219</v>
       </c>
@@ -3963,7 +3966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>220</v>
       </c>
@@ -3978,7 +3981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -3986,59 +3989,59 @@
       <c r="E80" s="2"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-    </row>
-    <row r="86" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="7"/>
-      <c r="B86" s="7"/>
-      <c r="C86" s="7"/>
-      <c r="D86" s="7"/>
-      <c r="E86" s="7"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A81" s="7"/>
+    </row>
+    <row r="86" spans="1:5" ht="31.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="D86" s="8"/>
+      <c r="E86" s="8"/>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="2"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="2"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="2"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="2"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="2"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="2"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="2"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A97" s="2"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A98" s="2"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A99" s="2"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A100" s="2"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A101" s="2"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A102" s="2"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A103" s="2"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A104" s="2"/>
     </row>
   </sheetData>
@@ -4055,16 +4058,16 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{279D9105-C626-4ED2-AE24-08E5CB5A9C68}">
   <dimension ref="A1:E41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="1" max="1" width="24.453125" customWidth="1"/>
+    <col min="2" max="2" width="31.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>71</v>
       </c>
@@ -4079,7 +4082,7 @@
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>76</v>
       </c>
@@ -4093,7 +4096,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>77</v>
       </c>
@@ -4105,7 +4108,7 @@
       </c>
       <c r="D3" s="2"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>79</v>
       </c>
@@ -4117,7 +4120,7 @@
       </c>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>80</v>
       </c>
@@ -4129,7 +4132,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>81</v>
       </c>
@@ -4141,7 +4144,7 @@
       </c>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>82</v>
       </c>
@@ -4151,7 +4154,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>84</v>
       </c>
@@ -4163,7 +4166,7 @@
       </c>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>85</v>
       </c>
@@ -4175,7 +4178,7 @@
       </c>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>87</v>
       </c>
@@ -4187,7 +4190,7 @@
       </c>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>89</v>
       </c>
@@ -4199,7 +4202,7 @@
       </c>
       <c r="D11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>91</v>
       </c>
@@ -4211,7 +4214,7 @@
       </c>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>96</v>
       </c>
@@ -4223,7 +4226,7 @@
       </c>
       <c r="D13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -4235,7 +4238,7 @@
       </c>
       <c r="D14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>99</v>
       </c>
@@ -4247,7 +4250,7 @@
       </c>
       <c r="D15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>100</v>
       </c>
@@ -4257,7 +4260,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>103</v>
       </c>
@@ -4269,7 +4272,7 @@
       </c>
       <c r="D17" s="2"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>105</v>
       </c>
@@ -4281,7 +4284,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>109</v>
       </c>
@@ -4293,7 +4296,7 @@
       </c>
       <c r="D19" s="2"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>120</v>
       </c>
@@ -4306,7 +4309,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>121</v>
       </c>
@@ -4318,7 +4321,7 @@
       </c>
       <c r="D21" s="2"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>122</v>
       </c>
@@ -4328,7 +4331,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>124</v>
       </c>
@@ -4340,7 +4343,7 @@
       </c>
       <c r="D23" s="2"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>126</v>
       </c>
@@ -4352,7 +4355,7 @@
       </c>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>127</v>
       </c>
@@ -4364,7 +4367,7 @@
       </c>
       <c r="D25" s="2"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>128</v>
       </c>
@@ -4376,7 +4379,7 @@
       </c>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>129</v>
       </c>
@@ -4386,7 +4389,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>130</v>
       </c>
@@ -4398,7 +4401,7 @@
       </c>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>131</v>
       </c>
@@ -4410,7 +4413,7 @@
       </c>
       <c r="D29" s="2"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>135</v>
       </c>
@@ -4422,7 +4425,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>137</v>
       </c>
@@ -4434,7 +4437,7 @@
       </c>
       <c r="D31" s="2"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>139</v>
       </c>
@@ -4446,7 +4449,7 @@
       </c>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" ht="28.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>140</v>
       </c>
@@ -4458,7 +4461,7 @@
       </c>
       <c r="D33" s="2"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>149</v>
       </c>
@@ -4470,7 +4473,7 @@
       </c>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>150</v>
       </c>
@@ -4482,7 +4485,7 @@
       </c>
       <c r="D35" s="2"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>153</v>
       </c>
@@ -4494,7 +4497,7 @@
       </c>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>157</v>
       </c>
@@ -4506,7 +4509,7 @@
       </c>
       <c r="D37" s="2"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>82</v>
       </c>
@@ -4516,7 +4519,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>129</v>
       </c>
@@ -4526,7 +4529,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>213</v>
       </c>
@@ -4536,7 +4539,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>215</v>
       </c>
@@ -4557,14 +4560,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDAEBF7-04B9-49D9-A929-0F44294592F2}">
   <dimension ref="B2:B27"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B2" s="4" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
         <v>226</v>
       </c>
